--- a/新数据生成/关卡表/10090.xlsx
+++ b/新数据生成/关卡表/10090.xlsx
@@ -459,8 +459,8 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="13.2" customWidth="1" min="13" max="13"/>
     <col width="13.2" customWidth="1" min="14" max="14"/>
-    <col width="17.6" customWidth="1" min="15" max="15"/>
-    <col width="4.4" customWidth="1" min="16" max="16"/>
+    <col width="13.2" customWidth="1" min="15" max="15"/>
+    <col width="13.2" customWidth="1" min="16" max="16"/>
     <col width="4.4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -693,10 +693,14 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>角色平均等级</t>
-        </is>
-      </c>
-      <c r="P6" s="1" t="n"/>
+          <t>阵容强度</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>参考等级</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="n">
@@ -709,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-8.6</v>
+        <v>-4.9</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -741,7 +745,10 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -749,30 +756,30 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-8.6</v>
+        <v>-4.9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -781,7 +788,10 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -792,23 +802,23 @@
         <v>2003</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-8.6</v>
+        <v>-4.9</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -821,7 +831,10 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -835,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
@@ -845,10 +858,10 @@
         <v>1.2</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>14.6</v>
+        <v>18.7</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -861,7 +874,10 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -869,30 +885,30 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>14.6</v>
+        <v>18.7</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精射手</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -901,47 +917,37 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="n">
-        <v>14.6</v>
+        <v>18.7</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>精射手</t>
-        </is>
-      </c>
+        <v>6.1</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>9</v>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -949,39 +955,42 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>21.7</v>
+        <v>15.3</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-8.5</v>
+        <v>-4.8</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -992,23 +1001,23 @@
         <v>2003</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>21.7</v>
+        <v>15.3</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-8.5</v>
+        <v>-4.8</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -1017,11 +1026,14 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1029,39 +1041,42 @@
         <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>21.7</v>
+        <v>15.3</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-8.5</v>
+        <v>-4.8</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1069,39 +1084,42 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1109,79 +1127,69 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5.4</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>9</v>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1192,23 +1200,23 @@
         <v>2001</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5.7</v>
+        <v>-8</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1221,38 +1229,45 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>2003</v>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3999</t>
+        </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>49464</v>
+      </c>
       <c r="I20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5.7</v>
+        <v>-8</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>技能Boss1</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1261,51 +1276,37 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>3998</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>188622</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>技能Boss2</t>
-        </is>
-      </c>
+        <v>-8</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>9</v>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1313,39 +1314,42 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>16.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>-7.7</v>
+        <v>-2.5</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1353,65 +1357,85 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>16.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>-7.7</v>
+        <v>-2.5</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K24" s="2" t="n">
-        <v>16.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+        <v>-2.5</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>泰森</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1422,23 +1446,23 @@
         <v>2002</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
         <v>0.6</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>21</v>
+        <v>18.2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -1451,7 +1475,10 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1459,30 +1486,30 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>21</v>
+        <v>18.2</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精射手</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1491,7 +1518,10 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1505,10 +1535,10 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="n">
-        <v>21</v>
+        <v>18.2</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
@@ -1516,8 +1546,9 @@
           <t>困难</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>9</v>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1528,10 +1559,10 @@
         <v>2001</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
@@ -1541,10 +1572,10 @@
         <v>1.2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>11.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>-4.6</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -1557,7 +1588,10 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1565,30 +1599,30 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>11.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>3</v>
+        <v>-4.6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -1597,47 +1631,37 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="n">
-        <v>11.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>泰森</t>
-        </is>
-      </c>
+        <v>-4.6</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>9</v>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1645,39 +1669,42 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>18.2</v>
+        <v>19.3</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-4.9</v>
+        <v>2</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>萨哈比精英坦克</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1685,39 +1712,42 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>18.2</v>
+        <v>19.3</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>-4.9</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>精射手</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -1731,19 +1761,20 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="n">
-        <v>18.2</v>
+        <v>19.3</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>-4.9</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>9</v>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1751,30 +1782,30 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>16.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>-1.3</v>
+        <v>1.9</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -1783,7 +1814,10 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -1791,13 +1825,13 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
@@ -1807,14 +1841,14 @@
         <v>1.2</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>16.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>-1.3</v>
+        <v>1.9</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -1823,7 +1857,10 @@
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1837,10 +1874,10 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="n">
-        <v>16.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>-1.3</v>
+        <v>1.9</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
@@ -1848,8 +1885,9 @@
           <t>一般</t>
         </is>
       </c>
-      <c r="O36" s="2" t="n">
-        <v>9</v>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1863,20 +1901,20 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -1889,7 +1927,10 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1897,30 +1938,30 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>垃圾刺客</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -1929,7 +1970,10 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1937,30 +1981,30 @@
         <v>11</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>4</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精射手</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -1969,7 +2013,10 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1977,30 +2024,30 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>20.6</v>
+        <v>23.2</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>-7.7</v>
+        <v>-5.3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2009,7 +2056,10 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2020,23 +2070,23 @@
         <v>2003</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>20.6</v>
+        <v>23.2</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>-7.7</v>
+        <v>-5.3</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -2049,33 +2099,53 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K42" s="2" t="n">
-        <v>20.6</v>
+        <v>23.2</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>-7.7</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+        <v>-5.3</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>影流之主</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2086,23 +2156,23 @@
         <v>2002</v>
       </c>
       <c r="F43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="G43" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>23.1</v>
+        <v>15.8</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -2115,7 +2185,10 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2123,30 +2196,30 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>23.1</v>
+        <v>15.8</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>垃圾刺客</t>
+          <t>精射手</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2155,33 +2228,53 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="D45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K45" s="2" t="n">
-        <v>23.1</v>
+        <v>15.8</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>刘易斯</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -2192,23 +2285,23 @@
         <v>2004</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-7.6</v>
+        <v>0.9</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -2217,11 +2310,14 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -2229,79 +2325,69 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>18.5</v>
+        <v>8</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>-7.6</v>
+        <v>0.9</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F48" s="2" t="n">
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G48" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" s="2" t="n">
-        <v>18.5</v>
-      </c>
       <c r="L48" s="2" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>9</v>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -2315,20 +2401,20 @@
         <v>3</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>19.8</v>
+        <v>17.6</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -2341,7 +2427,10 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -2349,30 +2438,30 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>19.8</v>
+        <v>17.6</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>垃圾刺客</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -2381,7 +2470,10 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -2389,30 +2481,30 @@
         <v>15</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>19.8</v>
+        <v>17.6</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>2.2</v>
+        <v>7.5</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>垃圾刺客</t>
+          <t>刘易斯</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -2421,7 +2513,10 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -2429,30 +2524,30 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>12.9</v>
+        <v>7</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-4.6</v>
+        <v>-0.9</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -2461,7 +2556,10 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -2469,30 +2567,30 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>12.9</v>
+        <v>7</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>-4.6</v>
+        <v>-0.9</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -2501,33 +2599,53 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K54" s="2" t="n">
-        <v>12.9</v>
+        <v>7</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+        <v>-0.9</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>残酷射手</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -2538,23 +2656,23 @@
         <v>2008</v>
       </c>
       <c r="F55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>10</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>-0.9</v>
+        <v>-5.4</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -2563,11 +2681,14 @@
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2578,23 +2699,23 @@
         <v>2004</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>-0.9</v>
+        <v>-5.4</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
@@ -2603,51 +2724,41 @@
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>2003</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="n">
-        <v>11.8</v>
+        <v>20</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>泰森</t>
-        </is>
-      </c>
+        <v>-5.4</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="n">
-        <v>9</v>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -2655,39 +2766,42 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>22.3</v>
+        <v>10.2</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>-9.5</v>
+        <v>1.1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2698,23 +2812,23 @@
         <v>2004</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>22.3</v>
+        <v>10.2</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>-9.5</v>
+        <v>1.1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
@@ -2723,11 +2837,14 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2741,19 +2858,20 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="n">
-        <v>22.3</v>
+        <v>10.2</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>-9.5</v>
+        <v>1.1</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>9</v>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -2761,39 +2879,42 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>9.6</v>
+        <v>23.3</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>4.5</v>
+        <v>-4.3</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -2801,65 +2922,85 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>9.6</v>
+        <v>23.3</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4.5</v>
+        <v>-4.3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="D63" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K63" s="2" t="n">
-        <v>9.6</v>
+        <v>23.3</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+        <v>-4.3</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>残酷射手</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O63" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -2867,30 +3008,30 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>8.1</v>
+        <v>11.2</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-4.5</v>
+        <v>-4.9</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -2899,7 +3040,10 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2910,23 +3054,23 @@
         <v>2003</v>
       </c>
       <c r="F65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" s="2" t="n">
         <v>6</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>13</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>8.1</v>
+        <v>11.2</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>-4.5</v>
+        <v>-4.9</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -2939,7 +3083,10 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2947,30 +3094,30 @@
         <v>20</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J66" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J66" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K66" s="2" t="n">
-        <v>8.1</v>
+        <v>11.2</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>-4.5</v>
+        <v>-4.9</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -2979,7 +3126,10 @@
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>9</v>
+        <v>4.4</v>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
